--- a/my-eng-bot/CEFR_Levels.xlsx
+++ b/my-eng-bot/CEFR_Levels.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PromptRules" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Levels_Config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,12 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,19 +414,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -448,7 +430,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Словарный запас</t>
+          <t>Словарный_запас</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -478,569 +460,497 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Грамматика (ключевое)</t>
+          <t>Грамматика_ключевое</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>AllowedVocabulary</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>AvoidVocabulary</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ForbiddenOrStrictlyLimited</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SentenceLengthGuideline</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>QuestionStyle</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>CorrectionPriority</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Survival/Beginner</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>&lt;1500</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Понимает знакомые слова и базовые фразы при медленной четкой речи</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Узнает знакомые имена/слова и простые предложения</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Поддерживает очень простой разговор при помощи собеседника</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Описывает себя, место жительства, близкое окружение простыми фразами</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Подписывает открытку, заполняет базовые анкеты</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Артикли (базово), формы глагола, неправильные глаголы (база), Present/Past/Future Simple (знакомство)</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Семья, дом, еда, школа, хобби, распорядок, базовые глаголы и прилагательные</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Абстрактные термины, редкие синонимы, идиомы, фразеологизмы</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>C1/C2 лексика, сложные клише, длинные академические слова</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Короткие фразы, 1 идея на предложение</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Короткие прямые вопросы о личном опыте и быте</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Сначала базовая грамматика (to be, порядок слов, артикли), затем лексика</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Waystage/Elementary</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>1500-2500</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Понимает часто употребимые слова и короткие простые высказывания</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Читает короткие бытовые тексты (меню, расписания, объявления), простые письма</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Ведет короткие диалоги в типичных жизненных ситуациях</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Кратко рассказывает о себе, семье, жилье, учебе, работе</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Пишет короткие записки/сообщения и простые личные письма</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Simple/Continuous/Perfect (базово), модальные глаголы (база), актив/пассив (база), условные (представление), степени сравнения</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Повседневная лексика + простые описательные слова и базовые слова мнения</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Узкоспециальная терминология, перегруженные формулировки</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Высокоабстрактная лексика, редкие идиомы</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Короткие/средние фразы, простые связки and/but/because</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Вопросы о планах, недавних событиях, предпочтениях</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Сначала времена Simple/Continuous (база), затем точность слов</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Threshold/Intermediate</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>2750-3250</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Понимает общий смысл рассказов на знакомые темы, большинство программ о текущих событиях</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Понимает повседневные тексты и письма с описанием событий/чувств</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Общается в большинстве ситуаций в поездке без подготовки</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Рассказывает о событиях, планах, обосновывает мнение</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Пишет простой связный текст и личные письма о событиях</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Present/Past/Future + Simple/Continuous/Perfect, Conditionals 1-3, infinitive/gerund, modals, reported speech, active/passive, used to, be going to</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Широкая повседневная лексика для мнений, причин, опыта</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Избыточно формальный академический стиль</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Редкие C2-идиомы без необходимости</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Средняя длина, ясная структура</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Вопросы с why/how + короткое объяснение</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>Сначала смысл и корректность времени, затем стиль</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Vantage/Upper-Intermediate</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>3250-3750</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Понимает длинные речи/дискуссии и большинство новостных программ</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Читает публицистику и неадаптированную прозу</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Уверенно общается с носителями, активно участвует в дискуссии</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Дает подробные описания, аргументирует плюсы/минусы</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>Пишет подробные тексты, эссе/отчеты, личные и несложные официальные письма</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>Уверенное владение всеми ключевыми временами и структурами B1 + стилистический контроль</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>Более точная тематическая лексика, естественные коллокации</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>Роботизированные и шаблонные фразы</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>Сверхсложные C2-архаизмы вне контекста</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>Средняя/длиннее средней, но без перегруза</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>Открытые нюансные вопросы, сравнение аргументов</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>Сначала точность формулировки, затем регистр</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>3750-4500</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Понимает развернутую речь даже при неявной структуре</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Понимает длинные сложные и специализированные тексты</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Говорит свободно, точно и эффективно в быту и профессии</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Дает ясные подробные описания сложных понятий, формулирует выводы</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>Пишет структурированные письма/эссе/доклады под целевую аудиторию</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>Свободное владение временами, модальность вероятности, инверсия в условных, вводные конструкции, средства связности</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Продвинутая точная лексика, дискурсивные маркеры, гибкий выбор регистра</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Чрезмерная упрощенность не по задаче</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Нерелевантная усложненность ради усложнения</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Гибкая длина по задаче</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Точные вопросы для анализа и рефлексии</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Сначала точность мысли и уместность регистра</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Proficiency</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>&gt;=4500</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Понимает практически любую устную речь, включая быструю</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Читает практически любые тексты, включая сложные абстрактные</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Участвует в любой беседе/дискуссии без трудностей, использует идиомы</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Строит ясный связный аргументированный монолог с четкой логикой</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>Пишет сложные логично структурированные письма/доклады/статьи, обзоры/резюме</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>Полный объем грамматики английского языка</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="61" customWidth="1" min="3" max="3"/>
-    <col width="59" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Уровень</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>AllowedVocabulary</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AvoidVocabulary</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ForbiddenOrStrictlyLimited</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SentenceLengthGuideline</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>QuestionStyle</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>CorrectionPriority</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Семья, дом, еда, школа, хобби, распорядок, базовые глаголы и прилагательные</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Абстрактные термины, редкие синонимы, идиомы, фразеологизмы</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>C1/C2 лексика, сложные клише, длинные академические слова</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Короткие фразы, 1 идея на предложение</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Короткие прямые вопросы о личном опыте и быте</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Сначала базовая грамматика (to be, порядок слов, артикли), затем лексика</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Повседневная лексика + простые описательные слова и базовые слова мнения</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Узкоспециальная терминология, перегруженные формулировки</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Высокоабстрактная лексика, редкие идиомы</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Короткие/средние фразы, простые связки and/but/because</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Вопросы о планах, недавних событиях, предпочтениях</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Сначала времена Simple/Continuous (база), затем точность слов</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Широкая повседневная лексика для мнений, причин, опыта</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Избыточно формальный академический стиль</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Редкие C2-идиомы без необходимости</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Средняя длина, ясная структура</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Вопросы с why/how + короткое объяснение</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Сначала смысл и корректность времени, затем стиль</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Более точная тематическая лексика, естественные коллокации</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Роботизированные и шаблонные фразы</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Сверхсложные C2-архаизмы вне контекста</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Средняя/длиннее средней, но без перегруза</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Открытые нюансные вопросы, сравнение аргументов</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Сначала точность формулировки, затем регистр</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Продвинутая точная лексика, дискурсивные маркеры, гибкий выбор регистра</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Чрезмерная упрощенность не по задаче</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Нерелевантная усложненность ради усложнения</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Гибкая длина по задаче</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Точные вопросы для анализа и рефлексии</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Сначала точность мысли и уместность регистра</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>Почти полный диапазон, включая идиомы и тонкие оттенки значений</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>Избыточная тяжеловесность без пользы</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>Нет формальных запретов, кроме неуместности</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="M7" s="1" t="inlineStr">
         <is>
           <t>Гибко, по риторической задаче</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>Тонко настраиваемые вопросы под контекст</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="O7" s="1" t="inlineStr">
         <is>
           <t>Сначала прагматика, стиль и естественность</t>
         </is>
